--- a/diseases/d017/2000-2004.xlsx
+++ b/diseases/d017/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2232,9 +2226,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3155,9 +3146,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -4078,9 +4066,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -5001,9 +4986,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5924,9 +5906,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -6847,9 +6826,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7770,9 +7746,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8693,9 +8666,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9616,9 +9586,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10539,9 +10506,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -11462,9 +11426,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -12385,9 +12346,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12929,9 +12887,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13556,9 +13511,6 @@
       <c r="O71" t="n">
         <v>7437</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>15.8087834850951</v>
       </c>
@@ -13704,9 +13656,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14248,9 +14197,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -15023,9 +14969,6 @@
       <c r="O79" t="n">
         <v>2432</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>5.169686894682169</v>
       </c>
@@ -15171,9 +15114,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15715,9 +15655,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -16490,9 +16427,6 @@
       <c r="O87" t="n">
         <v>3003</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>6.383457954247761</v>
       </c>
@@ -16638,9 +16572,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -17182,9 +17113,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17957,9 +17885,6 @@
       <c r="O95" t="n">
         <v>4708</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>10.00776558394887</v>
       </c>
@@ -18105,9 +18030,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18649,9 +18571,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -19424,9 +19343,6 @@
       <c r="O103" t="n">
         <v>3901</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>8.292330829011162</v>
       </c>
@@ -19572,9 +19488,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -20116,9 +20029,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -20891,9 +20801,6 @@
       <c r="O111" t="n">
         <v>1298</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>2.759150324546651</v>
       </c>
@@ -21039,9 +20946,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -21583,9 +21487,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -22358,9 +22259,6 @@
       <c r="O119" t="n">
         <v>212</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.4506470483851233</v>
       </c>
@@ -22506,9 +22404,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -23050,9 +22945,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -23825,9 +23717,6 @@
       <c r="O127" t="n">
         <v>32</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.06802219598266013</v>
       </c>
@@ -23973,9 +23862,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -24517,9 +24403,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -25292,9 +25175,6 @@
       <c r="O135" t="n">
         <v>6</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.01275416174674877</v>
       </c>
@@ -25440,9 +25320,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -25984,9 +25861,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26759,9 +26633,6 @@
       <c r="O143" t="n">
         <v>9</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.01913124262012316</v>
       </c>
@@ -26907,9 +26778,6 @@
       <c r="O144" t="n">
         <v>2</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -27451,9 +27319,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -28226,9 +28091,6 @@
       <c r="O151" t="n">
         <v>16</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.03401109799133006</v>
       </c>
@@ -28374,9 +28236,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -28918,9 +28777,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -29693,9 +29549,6 @@
       <c r="O159" t="n">
         <v>6</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.01275416174674877</v>
       </c>
@@ -29841,9 +29694,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -30385,9 +30235,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -30929,9 +30776,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -31325,9 +31169,6 @@
       <c r="O168" t="n">
         <v>6</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.0126852252992738</v>
       </c>
@@ -31473,9 +31314,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -32017,9 +31855,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -32561,9 +32396,6 @@
       <c r="O175" t="n">
         <v>6</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.0126852252992738</v>
       </c>
@@ -32709,9 +32541,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -33253,9 +33082,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -33797,9 +33623,6 @@
       <c r="O182" t="n">
         <v>7</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.01479942951581943</v>
       </c>
@@ -33945,9 +33768,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -34489,9 +34309,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -35033,9 +34850,6 @@
       <c r="O189" t="n">
         <v>7</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.01479942951581943</v>
       </c>
@@ -35181,9 +34995,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -35725,9 +35536,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -36269,9 +36077,6 @@
       <c r="O196" t="n">
         <v>8</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.01691363373236507</v>
       </c>
@@ -36417,9 +36222,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -36961,9 +36763,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -37505,9 +37304,6 @@
       <c r="O203" t="n">
         <v>5</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -37653,9 +37449,6 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -38197,9 +37990,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -38741,9 +38531,6 @@
       <c r="O210" t="n">
         <v>4</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.008456816866182533</v>
       </c>
@@ -38889,9 +38676,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -39433,9 +39217,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -39977,9 +39758,6 @@
       <c r="O217" t="n">
         <v>3</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -40125,9 +39903,6 @@
       <c r="O218" t="n">
         <v>2</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -40669,9 +40444,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -41213,9 +40985,6 @@
       <c r="O224" t="n">
         <v>4</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.008456816866182533</v>
       </c>
@@ -41361,9 +41130,6 @@
       <c r="O225" t="n">
         <v>1</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -41905,9 +41671,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -42449,9 +42212,6 @@
       <c r="O231" t="n">
         <v>8</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.01691363373236507</v>
       </c>
@@ -42597,9 +42357,6 @@
       <c r="O232" t="n">
         <v>1</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -43141,9 +42898,6 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -43685,9 +43439,6 @@
       <c r="O238" t="n">
         <v>1</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -43833,9 +43584,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -44377,9 +44125,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -44921,9 +44666,6 @@
       <c r="O245" t="n">
         <v>3</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -45069,9 +44811,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -45613,9 +45352,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -46157,9 +45893,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -46553,9 +46286,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -46701,9 +46431,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -47245,9 +46972,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -47789,9 +47513,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -47937,9 +47658,6 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -48481,9 +48199,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -49025,9 +48740,6 @@
       <c r="O268" t="n">
         <v>5</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -49173,9 +48885,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -49717,9 +49426,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -50261,9 +49967,6 @@
       <c r="O275" t="n">
         <v>2</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -50409,9 +50112,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -51101,9 +50801,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -51645,9 +51342,6 @@
       <c r="O283" t="n">
         <v>5</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -51793,9 +51487,6 @@
       <c r="O284" t="n">
         <v>2</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -52485,9 +52176,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -53029,9 +52717,6 @@
       <c r="O291" t="n">
         <v>4</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0.008418542931006853</v>
       </c>
@@ -53177,9 +52862,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -53721,9 +53403,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -54265,9 +53944,6 @@
       <c r="O298" t="n">
         <v>1</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -54413,9 +54089,6 @@
       <c r="O299" t="n">
         <v>3</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -54957,9 +54630,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -55501,9 +55171,6 @@
       <c r="O305" t="n">
         <v>2</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -55649,9 +55316,6 @@
       <c r="O306" t="n">
         <v>2</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -56193,9 +55857,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -56737,9 +56398,6 @@
       <c r="O312" t="n">
         <v>2</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -56885,9 +56543,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -57577,9 +57232,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -58121,9 +57773,6 @@
       <c r="O320" t="n">
         <v>3</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -58269,9 +57918,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -58961,9 +58607,6 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -59505,9 +59148,6 @@
       <c r="O328" t="n">
         <v>3</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -59653,9 +59293,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -60345,9 +59982,6 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0</v>
       </c>
@@ -60889,9 +60523,6 @@
       <c r="O336" t="n">
         <v>5</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -61037,9 +60668,6 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
@@ -61581,9 +61209,6 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
@@ -62125,9 +61750,6 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0</v>
       </c>
@@ -62521,9 +62143,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -62669,9 +62288,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -63213,9 +62829,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -63757,9 +63370,6 @@
       <c r="O352" t="n">
         <v>2</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -63905,9 +63515,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -64449,9 +64056,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -64993,9 +64597,6 @@
       <c r="O359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0</v>
       </c>
@@ -65141,9 +64742,6 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
@@ -65685,9 +65283,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -66229,9 +65824,6 @@
       <c r="O366" t="n">
         <v>1</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -66377,9 +65969,6 @@
       <c r="O367" t="n">
         <v>4</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -66921,9 +66510,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -67465,9 +67051,6 @@
       <c r="O373" t="n">
         <v>4</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -67613,9 +67196,6 @@
       <c r="O374" t="n">
         <v>2</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -68157,9 +67737,6 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
@@ -68701,9 +68278,6 @@
       <c r="O380" t="n">
         <v>3</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -68849,9 +68423,6 @@
       <c r="O381" t="n">
         <v>1</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -69393,9 +68964,6 @@
       <c r="O384" t="n">
         <v>0</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0</v>
       </c>
@@ -69937,9 +69505,6 @@
       <c r="O387" t="n">
         <v>0</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0</v>
       </c>
@@ -70085,9 +69650,6 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0</v>
       </c>
@@ -70629,9 +70191,6 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0</v>
       </c>
@@ -71173,9 +70732,6 @@
       <c r="O394" t="n">
         <v>0</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0</v>
       </c>
@@ -71321,9 +70877,6 @@
       <c r="O395" t="n">
         <v>0</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0</v>
       </c>
@@ -71865,9 +71418,6 @@
       <c r="O398" t="n">
         <v>0</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0</v>
       </c>
@@ -72409,9 +71959,6 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0</v>
       </c>
@@ -72557,9 +72104,6 @@
       <c r="O402" t="n">
         <v>0</v>
       </c>
-      <c r="Q402" t="n">
-        <v>0</v>
-      </c>
       <c r="R402" t="n">
         <v>0</v>
       </c>
@@ -73101,9 +72645,6 @@
       <c r="O405" t="n">
         <v>0</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0</v>
       </c>
@@ -73645,9 +73186,6 @@
       <c r="O408" t="n">
         <v>0</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0</v>
       </c>
@@ -73793,9 +73331,6 @@
       <c r="O409" t="n">
         <v>0</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0</v>
       </c>
@@ -74337,9 +73872,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -74881,9 +74413,6 @@
       <c r="O415" t="n">
         <v>0</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0</v>
       </c>
@@ -75029,9 +74558,6 @@
       <c r="O416" t="n">
         <v>0</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0</v>
       </c>
@@ -75573,9 +75099,6 @@
       <c r="O419" t="n">
         <v>0</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0</v>
       </c>
@@ -76117,9 +75640,6 @@
       <c r="O422" t="n">
         <v>1</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -76263,9 +75783,6 @@
         <v>0</v>
       </c>
       <c r="O423" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q423" t="n">
         <v>0</v>
       </c>
       <c r="R423" t="n">
